--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487191_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487191_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7818</v>
+        <v>4.77</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9562</v>
+        <v>5.185</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8256</v>
+        <v>-0.415</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8591</v>
+        <v>3.9404</v>
       </c>
       <c r="H2" t="n">
-        <v>2.425</v>
+        <v>3.3235</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4341</v>
+        <v>0.6169</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7449</v>
+        <v>4.5807</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0181</v>
+        <v>3.2705</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7268</v>
+        <v>1.3102</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1142</v>
+        <v>-0.6403</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4069</v>
+        <v>0.053</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2928</v>
+        <v>-0.6933</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.1231</v>
+        <v>0.386</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.0532</v>
+        <v>-1.158</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5546</v>
+        <v>-1.9701</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4225</v>
+        <v>-0.6514</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1321</v>
+        <v>-1.3187</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4912</v>
+        <v>2.4137</v>
       </c>
       <c r="W2" t="n">
-        <v>1.842</v>
+        <v>2.4137</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3156</v>
+        <v>4.5763</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2091</v>
+        <v>3.3093</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1065</v>
+        <v>1.2671</v>
       </c>
       <c r="G3" t="n">
         <v>4.3768</v>
@@ -688,13 +688,13 @@
         <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.1191</v>
+        <v>-1.8584</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8923</v>
+        <v>-0.7922</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2268</v>
+        <v>-1.0662</v>
       </c>
       <c r="V3" t="n">
         <v>0.8999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.309</v>
+        <v>3.4489</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8845</v>
+        <v>2.6681</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5756</v>
+        <v>0.7808</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9404</v>
+        <v>2.7102</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3235</v>
+        <v>1.118</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6169</v>
+        <v>1.5923</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5807</v>
+        <v>1.936</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2705</v>
+        <v>1.1385</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3102</v>
+        <v>0.7976</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6403</v>
+        <v>0.7742</v>
       </c>
       <c r="N4" t="n">
-        <v>0.053</v>
+        <v>-0.0205</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6933</v>
+        <v>0.7947</v>
       </c>
       <c r="P4" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.158</v>
+        <v>-2.1231</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.4311</v>
+        <v>-1.3312</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9518</v>
+        <v>-0.4584</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.4793</v>
+        <v>-0.8729</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4137</v>
+        <v>2.4559</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4137</v>
+        <v>3.3135</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2288</v>
+        <v>3.3917</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3677</v>
+        <v>3.155</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8611</v>
+        <v>0.2367</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7102</v>
+        <v>4.8591</v>
       </c>
       <c r="H5" t="n">
-        <v>1.118</v>
+        <v>2.425</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5923</v>
+        <v>2.4341</v>
       </c>
       <c r="J5" t="n">
-        <v>1.936</v>
+        <v>4.7449</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1385</v>
+        <v>2.0181</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7976</v>
+        <v>2.7268</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7742</v>
+        <v>0.1142</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0205</v>
+        <v>0.4069</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7947</v>
+        <v>-0.2928</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.386</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1231</v>
+        <v>-4.0532</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5514</v>
+        <v>0.1646</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7588</v>
+        <v>0.6214</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7926</v>
+        <v>-0.4568</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4559</v>
+        <v>0.4912</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3135</v>
+        <v>1.842</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8576</v>
+        <v>-1.3508</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.121</v>
+        <v>1.5622</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5806</v>
+        <v>2.7809</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4597</v>
+        <v>-1.2187</v>
       </c>
       <c r="G6" t="n">
         <v>1.6274</v>
@@ -922,13 +922,13 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8348</v>
+        <v>-0.3936</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2062</v>
+        <v>0.4065</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0411</v>
+        <v>-0.8001</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0226</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2818</v>
+        <v>0.7091</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4279</v>
+        <v>-1.0274</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7097</v>
+        <v>1.7365</v>
       </c>
       <c r="G7" t="n">
         <v>0.6944</v>
@@ -1000,13 +1000,13 @@
         <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9617</v>
+        <v>-0.5344</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4019</v>
+        <v>-0.0013</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5599</v>
+        <v>-0.5331</v>
       </c>
       <c r="V7" t="n">
         <v>0.1631</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5563</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6014</v>
+        <v>-0.2009</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9549</v>
+        <v>-0.7139</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2627</v>
@@ -1078,13 +1078,13 @@
         <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.4516</v>
+        <v>-1.8101</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9518</v>
+        <v>-0.5512</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.4998</v>
+        <v>-1.2589</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2137</v>
+        <v>-2.3743</v>
       </c>
       <c r="E9" t="n">
         <v>-2.7326</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5189</v>
+        <v>0.3583</v>
       </c>
       <c r="G9" t="n">
         <v>0.09320000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1018</v>
+        <v>-0.0588</v>
       </c>
       <c r="T9" t="n">
         <v>0.2657</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.164</v>
+        <v>-0.3246</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6366</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6682</v>
+        <v>-4.9815</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9948</v>
+        <v>-3.4955</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6734</v>
+        <v>-1.486</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3847</v>
@@ -1234,13 +1234,13 @@
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.3232</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7998</v>
+        <v>0.2991</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8097</v>
+        <v>-0.6223</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3085</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1712</v>
+        <v>-5.7592</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1579</v>
+        <v>-2.5585</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0133</v>
+        <v>-3.2007</v>
       </c>
       <c r="G11" t="n">
         <v>0.0625</v>
@@ -1312,13 +1312,13 @@
         <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9406</v>
+        <v>-1.5285</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1652</v>
+        <v>-0.5658</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7754</v>
+        <v>-0.9628</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1701</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.428600000000002</v>
+        <v>4.428400000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>7.083500000000001</v>
+        <v>7.083399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6551</v>
+        <v>-2.6549</v>
       </c>
       <c r="G12" t="n">
         <v>15.7166</v>
@@ -1366,7 +1366,7 @@
         <v>13.1112</v>
       </c>
       <c r="K12" t="n">
-        <v>8.181000000000001</v>
+        <v>8.180999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>4.9303</v>
@@ -1390,13 +1390,13 @@
         <v>13.5107</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.643800000000001</v>
+        <v>-9.643699999999999</v>
       </c>
       <c r="T12" t="n">
         <v>-1.4276</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.2165</v>
+        <v>-8.2164</v>
       </c>
       <c r="V12" t="n">
         <v>0.2859999999999996</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.3877</v>
+        <v>5.6774</v>
       </c>
       <c r="E13" t="n">
-        <v>6.3682</v>
+        <v>5.1665</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0195</v>
+        <v>0.5109</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7572</v>
@@ -1468,13 +1468,13 @@
         <v>2.5091</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1292</v>
+        <v>2.4189</v>
       </c>
       <c r="T13" t="n">
-        <v>3.0234</v>
+        <v>1.8217</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1058</v>
+        <v>0.5972</v>
       </c>
       <c r="V13" t="n">
         <v>2.6996</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2281</v>
+        <v>3.4719</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1838</v>
+        <v>3.4814</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0444</v>
+        <v>-0.0095</v>
       </c>
       <c r="G14" t="n">
         <v>2.642</v>
@@ -1546,13 +1546,13 @@
         <v>2.1231</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7485</v>
+        <v>1.9922</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4544</v>
+        <v>1.752</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2941</v>
+        <v>0.2402</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1623</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7431</v>
+        <v>0.6895</v>
       </c>
       <c r="E15" t="n">
         <v>0.09470000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6483</v>
+        <v>0.5948</v>
       </c>
       <c r="G15" t="n">
         <v>0.6148</v>
@@ -1624,13 +1624,13 @@
         <v>0.193</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0648</v>
+        <v>-0.1183</v>
       </c>
       <c r="T15" t="n">
         <v>0.074</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1388</v>
+        <v>-0.1924</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.171</v>
+        <v>0.2242</v>
       </c>
       <c r="E16" t="n">
         <v>0.074</v>
       </c>
       <c r="F16" t="n">
-        <v>0.097</v>
+        <v>0.1502</v>
       </c>
       <c r="G16" t="n">
         <v>0.3871</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2162</v>
+        <v>-0.1629</v>
       </c>
       <c r="T16" t="n">
         <v>0.074</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2902</v>
+        <v>-0.237</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2015</v>
+        <v>0.2196</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.9524</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0537</v>
+        <v>-0.7328</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3062</v>
@@ -1780,13 +1780,13 @@
         <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3021</v>
+        <v>0.7231</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4442</v>
+        <v>0.5443</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1421</v>
+        <v>0.1788</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1623</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.914</v>
+        <v>-1.3928</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3482</v>
+        <v>-2.1479</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4341</v>
+        <v>0.7551</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6014</v>
@@ -1858,13 +1858,13 @@
         <v>2.3161</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5096000000000001</v>
+        <v>1.0308</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4574</v>
+        <v>0.6577</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0522</v>
+        <v>0.3731</v>
       </c>
       <c r="V18" t="n">
         <v>0.7219</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>O. IBARROLA ITURRIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9881</v>
+        <v>-2.6139</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2272</v>
+        <v>1.0463</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7609</v>
+        <v>-3.6602</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3432</v>
+        <v>-3.0295</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6509</v>
+        <v>-0.1149</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3077</v>
+        <v>-2.9146</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9892</v>
+        <v>0.374</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0299</v>
+        <v>1.7749</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0407</v>
+        <v>-1.4009</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3539</v>
+        <v>-3.4035</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.621</v>
+        <v>-1.8898</v>
       </c>
       <c r="O19" t="n">
-        <v>0.267</v>
+        <v>-1.5137</v>
       </c>
       <c r="P19" t="n">
-        <v>0.579</v>
+        <v>1.9301</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="R19" t="n">
-        <v>0.579</v>
+        <v>2.1231</v>
       </c>
       <c r="S19" t="n">
-        <v>0.232</v>
+        <v>1.1194</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.238</v>
+        <v>0.8653</v>
       </c>
       <c r="U19" t="n">
-        <v>0.47</v>
+        <v>0.2541</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.4559</v>
+        <v>-2.6339</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4559</v>
+        <v>-2.6339</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. PEREZ PEREZ</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6929</v>
+        <v>-2.8751</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6563</v>
+        <v>-0.9268</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0366</v>
+        <v>-1.9483</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.0741</v>
+        <v>-1.3432</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.3583</v>
+        <v>-1.6509</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7158</v>
+        <v>0.3077</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.3651</v>
+        <v>-0.9892</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.4301</v>
+        <v>-1.0299</v>
       </c>
       <c r="L20" t="n">
-        <v>0.065</v>
+        <v>0.0407</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7091</v>
+        <v>-0.3539</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9283</v>
+        <v>-0.621</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7808</v>
+        <v>0.267</v>
       </c>
       <c r="P20" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9301</v>
+        <v>0.579</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7093</v>
+        <v>0.345</v>
       </c>
       <c r="T20" t="n">
-        <v>1.125</v>
+        <v>0.0625</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5843</v>
+        <v>0.2826</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8999</v>
+        <v>-2.4559</v>
       </c>
       <c r="W20" t="n">
-        <v>2.7418</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.842</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. IBARROLA ITURRIA</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0433</v>
+        <v>-3.3616</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0449</v>
+        <v>-3.4294</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.0882</v>
+        <v>0.0678</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0295</v>
+        <v>-4.2489</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1149</v>
+        <v>-2.6695</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9146</v>
+        <v>-1.5794</v>
       </c>
       <c r="J21" t="n">
-        <v>0.374</v>
+        <v>-2.3275</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7749</v>
+        <v>-1.5943</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4009</v>
+        <v>-0.7333</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.4035</v>
+        <v>-1.9214</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8898</v>
+        <v>-1.0752</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5137</v>
+        <v>-0.8461</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9301</v>
+        <v>-3.2811</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.193</v>
+        <v>-5.9833</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1231</v>
+        <v>2.7021</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.31</v>
+        <v>1.361</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1361</v>
+        <v>1.2397</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1739</v>
+        <v>0.1213</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.6339</v>
+        <v>2.8074</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.6417</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.6339</v>
+        <v>-0.8342000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>A. PEREZ PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1185</v>
+        <v>-3.8</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7312</v>
+        <v>-1.6563</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3873</v>
+        <v>-2.1437</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.2489</v>
+        <v>-7.0741</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6695</v>
+        <v>-5.3583</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5794</v>
+        <v>-1.7158</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3275</v>
+        <v>-4.3651</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5943</v>
+        <v>-4.4301</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7333</v>
+        <v>0.065</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9214</v>
+        <v>-2.7091</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0752</v>
+        <v>-0.9283</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8461</v>
+        <v>-1.7808</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.2811</v>
+        <v>0.772</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.9833</v>
+        <v>-1.158</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7021</v>
+        <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3959</v>
+        <v>1.6022</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0621</v>
+        <v>1.125</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3338</v>
+        <v>0.4772</v>
       </c>
       <c r="V22" t="n">
-        <v>2.8074</v>
+        <v>0.8999</v>
       </c>
       <c r="W22" t="n">
-        <v>3.6417</v>
+        <v>2.7418</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.428400000000001</v>
+        <v>-3.7608</v>
       </c>
       <c r="E23" t="n">
-        <v>2.654999999999998</v>
+        <v>2.6549</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.083399999999999</v>
+        <v>-6.4157</v>
       </c>
       <c r="G23" t="n">
         <v>-15.7166</v>
@@ -2218,13 +2218,13 @@
         <v>-8.911899999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-6.8046</v>
+        <v>-6.804599999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.605300000000001</v>
+        <v>-2.6053</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7312000000000014</v>
+        <v>-0.7312000000000007</v>
       </c>
       <c r="L23" t="n">
         <v>-1.8742</v>
@@ -2248,16 +2248,16 @@
         <v>15.4406</v>
       </c>
       <c r="S23" t="n">
-        <v>9.643800000000001</v>
+        <v>10.3114</v>
       </c>
       <c r="T23" t="n">
         <v>8.216200000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4276</v>
+        <v>2.0951</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2856000000000001</v>
+        <v>-0.2856000000000006</v>
       </c>
       <c r="W23" t="n">
         <v>10.5547</v>
